--- a/analise_eua/semicondutores/broadcom/avgo_10q.xlsx
+++ b/analise_eua/semicondutores/broadcom/avgo_10q.xlsx
@@ -22,13 +22,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,13 +50,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,454 +433,475 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45872</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45781</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45690</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45508</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45417</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45326</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45137</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45046</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44955</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44773</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44682</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44591</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44409</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44318</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44227</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44045</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43954</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43863</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>19628</v>
+      </c>
+      <c r="C2" t="n">
         <v>14174</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>10718</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>9472</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>9307</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>9952</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>9809</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>11864</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>12055</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>11553</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>12647</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>9977</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>9005</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>10219</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>11105</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>9518</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9552</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>8857</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>9207</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>6444</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Accounts Receivable, after Allowance for Credit Loss, Current</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>10830</v>
+      </c>
+      <c r="C3" t="n">
         <v>8460</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>6494</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>5563</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>4955</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>4665</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>5500</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>4969</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2914</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>3031</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>3234</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>2708</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>3083</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2539</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>2234</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2425</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>2524</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>2684</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>3211</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>3651</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Inventory, Net</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>4328</v>
+      </c>
+      <c r="C4" t="n">
         <v>2962</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>2180</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>2017</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>1908</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1894</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1842</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1920</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1842</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>1886</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>1899</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1838</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1668</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>1520</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1160</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>1004</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>952</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>1081</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>953</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>944</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Other Assets, Current</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>7427</v>
+      </c>
+      <c r="C5" t="n">
         <v>6466</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>5606</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>5129</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>4820</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>3436</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>8151</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>8439</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1522</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>1401</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1056</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1038</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1054</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>1063</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1137</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>1298</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>1272</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>1059</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>851</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1070</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Assets, Current</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>42213</v>
+      </c>
+      <c r="C6" t="n">
         <v>32062</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>24998</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>22181</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>20990</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>19947</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>25302</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>27192</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>18333</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>17871</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>18836</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>15561</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>14810</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>15341</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>15636</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>14245</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>14300</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>13681</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>14222</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>12109</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment, Net</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>2788</v>
+      </c>
+      <c r="C7" t="n">
         <v>2599</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>2451</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>2462</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>2465</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>2602</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>2668</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>2662</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>2180</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>2209</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>2201</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>2250</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2262</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2303</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>2370</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>2416</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>2496</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>2567</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>2618</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>2616</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
@@ -881,37 +916,37 @@
         <v>97801</v>
       </c>
       <c r="E8" t="n">
+        <v>97801</v>
+      </c>
+      <c r="F8" t="n">
         <v>97871</v>
-      </c>
-      <c r="F8" t="n">
-        <v>97873</v>
       </c>
       <c r="G8" t="n">
         <v>97873</v>
       </c>
       <c r="H8" t="n">
+        <v>97873</v>
+      </c>
+      <c r="I8" t="n">
         <v>97586</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>43619</v>
-      </c>
-      <c r="J8" t="n">
-        <v>43614</v>
       </c>
       <c r="K8" t="n">
         <v>43614</v>
       </c>
       <c r="L8" t="n">
+        <v>43614</v>
+      </c>
+      <c r="M8" t="n">
         <v>43608</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>43603</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>43450</v>
-      </c>
-      <c r="O8" t="n">
-        <v>43457</v>
       </c>
       <c r="P8" t="n">
         <v>43457</v>
@@ -920,337 +955,355 @@
         <v>43457</v>
       </c>
       <c r="R8" t="n">
+        <v>43457</v>
+      </c>
+      <c r="S8" t="n">
         <v>43447</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>43457</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>43472</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Intangible Assets, Net (Excluding Goodwill)</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>28333</v>
+      </c>
+      <c r="C9" t="n">
         <v>30302</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>34344</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>36393</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>38583</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>43034</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>45407</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>47185</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>4654</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>5434</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>6225</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>8174</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>9241</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>10244</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>12719</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>14068</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>15419</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>18357</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>19909</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>21465</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Other Assets, Noncurrent</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>8023</v>
+      </c>
+      <c r="C10" t="n">
         <v>7139</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>6027</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>5793</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>5449</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>4510</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>3961</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>3245</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>2809</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>2539</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>2100</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1733</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>1803</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>1886</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>1698</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>1338</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>1300</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>1246</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>1342</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>1344</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>179158</v>
+      </c>
+      <c r="C11" t="n">
         <v>169903</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>165621</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>164630</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>165358</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>167966</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>175211</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>177870</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>71595</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>71667</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>72976</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>71326</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>71719</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>73224</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>75880</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>75524</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>76972</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>79298</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>81548</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>81006</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Accounts Payable, Current</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>2337</v>
+      </c>
+      <c r="C12" t="n">
         <v>2112</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>1432</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>1297</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>1905</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>1757</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>1441</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>1496</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>992</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>831</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>923</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>712</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1069</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>1078</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>968</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>830</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>898</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>1092</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>1230</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>985</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Employee-related Liabilities, Current</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>1134</v>
+      </c>
+      <c r="C13" t="n">
         <v>864</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>1719</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>1266</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>922</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>1725</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>1385</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>1128</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>831</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>634</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>536</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>1079</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>751</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>531</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>893</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>639</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>494</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>732</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>494</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>435</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Debt, Current</t>
         </is>
@@ -1259,17 +1312,17 @@
         <v>2252</v>
       </c>
       <c r="C14" t="n">
+        <v>2252</v>
+      </c>
+      <c r="D14" t="n">
         <v>1399</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>5531</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>5653</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
@@ -1312,430 +1365,451 @@
       <c r="T14" t="n">
         <v>0</v>
       </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Other Liabilities, Current</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>13139</v>
+      </c>
+      <c r="C15" t="n">
         <v>11631</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>12154</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>12503</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>12430</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>12578</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>14919</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>15312</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>4403</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>4929</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>4909</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>4607</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>4788</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>4378</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>4361</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>4689</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>4438</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>4056</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>4058</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>4008</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Liabilities, Current</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>18862</v>
+      </c>
+      <c r="C16" t="n">
         <v>16859</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>16704</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>20597</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>20910</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>19221</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>20171</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>20369</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>7345</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>7511</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>7483</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>6702</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>6910</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>6287</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>6501</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>6436</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>6694</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>6702</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>6601</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>7739</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Long-term Debt and Lease Obligation</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>62655</v>
+      </c>
+      <c r="C17" t="n">
         <v>63805</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>62830</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>61751</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>60926</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>66798</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>71590</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>73468</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>38222</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>38194</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>38167</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>39191</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>39164</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>39205</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>40178</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
         <v>41068</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>43201</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>45044</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>42407</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Other Liabilities, Noncurrent</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>9950</v>
+      </c>
+      <c r="C18" t="n">
         <v>9367</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>12810</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>12696</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>13733</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>16296</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>13489</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>13749</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>3949</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>3955</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>4016</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>4530</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>4655</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>4738</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>4834</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>4962</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>5211</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>5810</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>5933</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>6464</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Liabilities</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>91467</v>
+      </c>
+      <c r="C19" t="n">
         <v>90031</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>92344</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>95044</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>95569</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>102315</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>105250</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>107586</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>49516</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>49660</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>49666</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>50423</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>50729</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>50230</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>51513</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>51558</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>52973</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>55713</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>57578</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>56610</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Additional Paid in Capital</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>75312</v>
+      </c>
+      <c r="C20" t="n">
         <v>73135</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>69011</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>66689</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>66848</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>67313</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>69754</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>70077</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>20855</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>20826</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>21119</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>20990</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>21078</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>23083</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>24126</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>24045</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>24080</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>23688</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>24073</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>24500</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Retained Earnings (Accumulated Deficit)</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>12166</v>
+      </c>
+      <c r="C21" t="n">
         <v>6520</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>4040</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>2686</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>2729</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>-1875</v>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>1178</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>1363</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>2371</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -1743,11 +1817,11 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>320</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
@@ -1760,137 +1834,146 @@
       <c r="T21" t="n">
         <v>0</v>
       </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Accumulated Other Comprehensive Income (Loss), Net of Tax</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>208</v>
+      </c>
+      <c r="C22" t="n">
         <v>212</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>221</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>206</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>207</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>208</v>
-      </c>
-      <c r="G22" t="n">
-        <v>207</v>
       </c>
       <c r="H22" t="n">
         <v>207</v>
       </c>
       <c r="I22" t="n">
+        <v>207</v>
+      </c>
+      <c r="J22" t="n">
         <v>46</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>-182</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-180</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-114</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-115</v>
       </c>
       <c r="N22" t="n">
         <v>-115</v>
       </c>
       <c r="O22" t="n">
-        <v>-106</v>
+        <v>-115</v>
       </c>
       <c r="P22" t="n">
         <v>-106</v>
       </c>
       <c r="Q22" t="n">
+        <v>-106</v>
+      </c>
+      <c r="R22" t="n">
         <v>-107</v>
-      </c>
-      <c r="R22" t="n">
-        <v>-131</v>
       </c>
       <c r="S22" t="n">
         <v>-131</v>
       </c>
       <c r="T22" t="n">
+        <v>-131</v>
+      </c>
+      <c r="U22" t="n">
         <v>-132</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Total Shareholders Equity</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>87691</v>
+      </c>
+      <c r="C23" t="n">
         <v>79872</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>73277</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>69586</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>69789</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>65651</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>69961</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>70284</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>22079</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>22007</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>23310</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>20876</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>20963</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>22968</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>24340</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>23939</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>23973</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>23557</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>23942</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>24368</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Long-term Debt and Lease Obligation, Current</t>
         </is>
@@ -1908,48 +1991,51 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
         <v>3161</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>2426</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>2433</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>1119</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>1117</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>1115</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>304</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>302</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>300</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>279</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>278</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>864</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>822</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>819</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>2311</v>
       </c>
     </row>
@@ -1964,691 +2050,721 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45872</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45781</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45690</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45508</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45417</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45326</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45137</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45046</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44955</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44773</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44682</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44591</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44409</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44318</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44227</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44045</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43954</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43863</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Revenues</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>22187</v>
+      </c>
+      <c r="C2" t="n">
         <v>19311</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>15952</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>15004</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>14916</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>13072</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>12487</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>11961</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>8876</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>8733</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>8915</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>8464</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>8103</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>7706</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>6778</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>6610</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>6655</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>5821</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>5742</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>5858</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Cost Of Products Sold</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4665</v>
+      </c>
+      <c r="C3" t="n">
         <v>4041</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>3096</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>2720</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>2693</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>2434</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2429</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2160</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2107</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>2019</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>2225</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1921</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1798</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>1769</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1572</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>1548</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>1672</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>1383</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>1448</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1459</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Cost Of Subscriptions And Services</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>636</v>
+      </c>
+      <c r="C4" t="n">
         <v>638</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>608</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>576</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>580</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>699</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>713</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>954</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>165</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>158</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>149</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>156</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>158</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>156</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>157</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>151</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>142</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>154</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>144</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>177</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Amortization Of Acquisition Related Intangible Assets Cost Of Products Sold</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>1461</v>
+      </c>
+      <c r="C5" t="n">
         <v>1462</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>1519</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>1483</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1484</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1525</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1516</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1380</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>439</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>441</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>535</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>705</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>707</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>730</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>851</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>853</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>874</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>953</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>954</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>950</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Restructuring Charges Cost Of Products Sold</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="n">
         <v>13</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>26</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>28</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>14</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>58</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>53</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>92</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
         <v>2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>15</v>
       </c>
       <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="n">
         <v>7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Cost of Revenue</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>6772</v>
+      </c>
+      <c r="C7" t="n">
         <v>6154</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>5249</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>4807</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>4771</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>4716</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>4711</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>4586</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>2712</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>2618</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>2911</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>2783</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2664</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2657</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>2581</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>2553</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>2703</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>2505</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>2553</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>2594</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>15415</v>
+      </c>
+      <c r="C8" t="n">
         <v>13157</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>10703</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>10197</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>10145</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>8356</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>7776</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>7375</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6164</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>6115</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>6004</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>5681</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>5439</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>5049</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>4197</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>4057</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3952</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>3316</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>3189</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>3264</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Research and Development</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>2995</v>
+      </c>
+      <c r="C9" t="n">
         <v>2965</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>3050</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>2693</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>2253</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>2353</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>2415</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>2308</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1358</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>1312</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>1195</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1255</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1261</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>1206</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1205</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>1238</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1211</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>1228</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1269</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>1289</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Selling, General and Administrative Expense</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>1055</v>
+      </c>
+      <c r="C10" t="n">
         <v>1019</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>1072</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>1083</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>949</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>1100</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1277</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>1572</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>388</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>438</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>348</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>323</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>368</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>321</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>346</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>325</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>339</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>428</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>501</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>601</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Amortization Of Acquisition Related Intangible Assets Operating Expenses</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C11" t="n">
         <v>507</v>
       </c>
       <c r="D11" t="n">
+        <v>507</v>
+      </c>
+      <c r="E11" t="n">
         <v>506</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>511</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>812</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>827</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>792</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>350</v>
-      </c>
-      <c r="J11" t="n">
-        <v>348</v>
       </c>
       <c r="K11" t="n">
         <v>348</v>
       </c>
       <c r="L11" t="n">
+        <v>348</v>
+      </c>
+      <c r="M11" t="n">
         <v>359</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>398</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>397</v>
-      </c>
-      <c r="O11" t="n">
-        <v>494</v>
       </c>
       <c r="P11" t="n">
         <v>494</v>
@@ -2657,763 +2773,799 @@
         <v>494</v>
       </c>
       <c r="R11" t="n">
+        <v>494</v>
+      </c>
+      <c r="S11" t="n">
         <v>600</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>599</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>603</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Restructuring, Settlement and Impairment Provisions</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>71</v>
+      </c>
+      <c r="C12" t="n">
         <v>103</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>187</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>86</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>172</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>303</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>292</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>620</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>212</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>9</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>7</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>18</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>17</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>26</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>25</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>71</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>52</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>54</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Operating Expenses</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>4627</v>
+      </c>
+      <c r="C13" t="n">
         <v>4594</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>4816</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>4368</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>3885</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>4568</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>4811</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>5292</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>2308</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>2107</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>1901</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>1944</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>2045</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>1941</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>2071</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>2082</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>2115</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>2308</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>2423</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Operating Income</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>10788</v>
+      </c>
+      <c r="C14" t="n">
         <v>8563</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>5887</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>5829</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>6260</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>3788</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>2965</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>2083</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>3856</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>4008</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>4103</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>3737</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3394</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>3108</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>2126</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>1975</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>1837</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>1008</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>766</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>714</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>-776</v>
+      </c>
+      <c r="C15" t="n">
         <v>-801</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>-807</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>-769</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-873</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>-1064</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>-1047</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>-926</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>-406</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>-405</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-406</v>
       </c>
       <c r="L15" t="n">
         <v>-406</v>
       </c>
       <c r="M15" t="n">
+        <v>-406</v>
+      </c>
+      <c r="N15" t="n">
         <v>-518</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>-407</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>-415</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>-466</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>-570</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>-464</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>-487</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>-406</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Other Nonoperating Income (Expense)</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>118</v>
+      </c>
+      <c r="C16" t="n">
         <v>433</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>205</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>25</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>103</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>82</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>87</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>185</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>124</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>113</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>143</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>6</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>-86</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>-14</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>15</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>-23</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>117</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>49</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>130</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-4</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Income Before Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>10130</v>
+      </c>
+      <c r="C17" t="n">
         <v>8195</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>5285</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>5085</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>5490</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>2806</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>2005</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>1342</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>3574</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>3716</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>3840</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>3337</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>2790</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>2687</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1726</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>1486</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>1384</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>593</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>409</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>304</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>820</v>
+      </c>
+      <c r="C18" t="n">
         <v>846</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>1145</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>120</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-13</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>4238</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>-116</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>68</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>271</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>235</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>66</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>263</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>200</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>215</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>-150</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>-7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>6</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>-96</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-159</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-76</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Net Income (Loss), Including Portion Attributable to Noncontrolling Interest</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>9310</v>
+      </c>
+      <c r="C19" t="n">
         <v>7349</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>4140</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>4965</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>5503</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>-1875</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>2121</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1325</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>3303</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>3481</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>3774</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>3074</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>2590</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>2472</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>1876</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>1493</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>1378</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>688</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>563</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>385</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Earnings Per Share, Basic</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C20" t="n">
         <v>1.55</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>0.88</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>1.05</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>1.17</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>4.56</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>2.93</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>8</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>9.029999999999999</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>7.4</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>6.16</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>5.82</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>4.38</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>3.2</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>1.52</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>1.22</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>0.78</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Earnings Per Share, Diluted</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C21" t="n">
         <v>1.5</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>0.85</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>1.03</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>1.14</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>4.42</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>2.84</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>7.74</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>8.15</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>7.15</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>5.93</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>5.59</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>4.2</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>3.05</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>1.45</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>1.17</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>0.74</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Number of Shares - Basic</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>4747</v>
+      </c>
+      <c r="C22" t="n">
         <v>4741</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>4714</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>4707</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>4695</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>4663</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>465</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>452</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>413</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>415</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>418</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>405</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>408</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>412</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>411</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>409</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>407</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>403</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>401</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>398</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Number of Shares - Diluted</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>4876</v>
+      </c>
+      <c r="C23" t="n">
         <v>4888</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>4860</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>4826</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>4836</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>4663</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>480</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>467</v>
-      </c>
-      <c r="I23" t="n">
-        <v>427</v>
       </c>
       <c r="J23" t="n">
         <v>427</v>
       </c>
       <c r="K23" t="n">
+        <v>427</v>
+      </c>
+      <c r="L23" t="n">
         <v>429</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>430</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>424</v>
-      </c>
-      <c r="N23" t="n">
-        <v>429</v>
       </c>
       <c r="O23" t="n">
         <v>429</v>
@@ -3422,79 +3574,85 @@
         <v>429</v>
       </c>
       <c r="Q23" t="n">
+        <v>429</v>
+      </c>
+      <c r="R23" t="n">
         <v>428</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>422</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>417</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>420</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>9310</v>
+      </c>
+      <c r="C24" t="n">
         <v>7349</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>4140</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>4965</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>5503</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>-1875</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>2121</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>1325</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>3303</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>3481</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>3774</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2999</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>2515</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>2398</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>1802</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>1417</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>1304</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>614</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>488</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>311</v>
       </c>
     </row>
@@ -3509,412 +3667,430 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45872</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45781</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45690</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45508</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45417</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45326</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45137</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45046</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44955</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44773</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44682</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44591</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44409</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44318</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44227</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44045</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43954</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43863</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Net Income (Loss), Including Portion Attributable to Noncontrolling Interest</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>16659</v>
+      </c>
+      <c r="C2" t="n">
         <v>7349</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>14608</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>10468</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>5503</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1571</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>3446</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1325</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>10558</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>7255</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>3774</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>8136</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5062</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2472</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>4747</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>2871</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>1378</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>1636</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>948</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>385</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Amortization Of Intangible And Right Of Use Assets</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4005</v>
+      </c>
+      <c r="C3" t="n">
         <v>2003</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>6116</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>4056</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>2032</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>6962</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>4587</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2206</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2525</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>1715</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>905</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>3368</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2280</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>1151</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>4135</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2766</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>1395</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>4746</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>3165</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1582</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Depreciation, Depletion and Amortization</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>313</v>
+      </c>
+      <c r="C4" t="n">
         <v>150</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>426</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>284</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>142</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>437</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>288</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>139</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>378</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>256</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>127</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>400</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>271</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>136</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>405</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>271</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>138</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>431</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>293</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>146</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Share-based Payment Arrangement, Noncash Expense</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>4268</v>
+      </c>
+      <c r="C5" t="n">
         <v>2176</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>5373</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>3051</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1280</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>4427</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>3039</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1582</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1533</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>904</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>391</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1146</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>773</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>387</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1290</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>869</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>444</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>1527</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>1062</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>545</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Deferred Income Taxes And Other Non Cash Tax Expense</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>-1058</v>
+      </c>
+      <c r="C6" t="n">
         <v>-455</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>-983</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>-1267</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-696</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>2833</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-805</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>-294</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-1140</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>-889</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>-573</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>55</v>
-      </c>
-      <c r="M6" t="n">
-        <v>70</v>
       </c>
       <c r="N6" t="n">
         <v>70</v>
       </c>
       <c r="O6" t="n">
+        <v>70</v>
+      </c>
+      <c r="P6" t="n">
         <v>-762</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>-326</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>-149</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>-683</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-247</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>-72</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Gain (Loss) on Extinguishment of Debt</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>86</v>
+      </c>
+      <c r="C7" t="n">
         <v>55</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>118</v>
-      </c>
-      <c r="D7" t="n">
-        <v>65</v>
       </c>
       <c r="E7" t="n">
         <v>65</v>
       </c>
       <c r="F7" t="n">
+        <v>65</v>
+      </c>
+      <c r="G7" t="n">
         <v>105</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -3928,711 +4104,744 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>198</v>
       </c>
       <c r="Q7" t="n">
+        <v>198</v>
+      </c>
+      <c r="R7" t="n">
         <v>172</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>153</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>98</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Amortization of Debt Issuance Costs and Discounts</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>139</v>
+      </c>
+      <c r="C8" t="n">
         <v>72</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>273</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>191</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>97</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>336</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>221</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>102</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>98</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>65</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>32</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>97</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>65</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>32</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>67</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>43</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>22</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>83</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>61</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Other Noncash Income (Expense)</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>18</v>
+      </c>
+      <c r="C9" t="n">
         <v>15</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>58</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>81</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>41</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>266</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>130</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>38</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-18</v>
       </c>
       <c r="J9" t="n">
         <v>-18</v>
       </c>
       <c r="K9" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L9" t="n">
         <v>-39</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>12</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>10</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>-1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-8</v>
       </c>
       <c r="P9" t="n">
         <v>-8</v>
       </c>
       <c r="Q9" t="n">
+        <v>-8</v>
+      </c>
+      <c r="R9" t="n">
         <v>-5</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>-43</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>11</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Accounts Receivable</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-3685</v>
+      </c>
+      <c r="C10" t="n">
         <v>-1315</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>-2066</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>-1129</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-539</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>2078</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1243</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>1756</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>44</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-91</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-276</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-629</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-1004</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-468</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>50</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>-141</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>-247</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>590</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>48</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-392</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Inventories</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-2058</v>
+      </c>
+      <c r="C11" t="n">
         <v>-692</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>-420</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>-257</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-148</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>16</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>68</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-14</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>83</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>39</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>26</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>-540</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>-370</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>-223</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>-157</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>-1</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>51</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>-98</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>30</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Accounts Payable</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>683</v>
+      </c>
+      <c r="C12" t="n">
         <v>534</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>-236</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>-372</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>241</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>206</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-167</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-74</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-6</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>-194</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-80</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-383</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>-31</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
       <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>142</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>-14</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>44</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>227</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>350</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>117</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Employee Related Liabilities</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>-991</v>
+      </c>
+      <c r="C13" t="n">
         <v>-1261</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>-110</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>-621</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>-908</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>-118</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>-409</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>-660</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-382</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>-566</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>-657</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>8</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-313</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>-528</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>14</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>-240</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>-375</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>75</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-156</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-217</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Current Assets and Liabilities, Net</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>-218</v>
+      </c>
+      <c r="C14" t="n">
         <v>-692</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>-1028</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>-29</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>26</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>-3913</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>-2568</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>-2182</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>66</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>405</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>570</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>610</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>808</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>521</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>363</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>590</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>408</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>462</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>464</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>346</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Noncurrent Assets and Liabilities, Net</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>592</v>
+      </c>
+      <c r="C15" t="n">
         <v>321</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>-2295</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>-1853</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-1023</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>-848</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>322</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>891</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>-482</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>-343</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-164</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>-367</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>-107</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>-79</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>-206</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>-129</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>-59</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>-425</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>-609</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>-223</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Operating Activities</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>18753</v>
+      </c>
+      <c r="C16" t="n">
         <v>8260</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>19834</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>12668</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>6113</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>14358</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>9395</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>4815</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>13257</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>8538</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>4036</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>12153</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>7729</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>3486</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>10223</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>6682</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>3113</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>8713</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>5535</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>2322</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Payments to Acquire Property, Plant, and Equipment</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>-481</v>
+      </c>
+      <c r="C17" t="n">
         <v>-250</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>-386</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>-244</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>-100</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>-426</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-254</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-122</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-347</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>-225</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>-103</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>-302</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-186</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>-101</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>-355</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>-240</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>-114</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>-361</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-256</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-108</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Payments to Acquire Investments</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>-137</v>
+      </c>
+      <c r="C18" t="n">
         <v>-114</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>-261</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>-162</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-105</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>-145</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>-72</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>-13</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>-288</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>-197</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>-200</v>
@@ -4641,7 +4850,7 @@
         <v>-200</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4658,58 +4867,61 @@
       <c r="T18" t="n">
         <v>0</v>
       </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Sale, Maturity and Collection of Investments</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>283</v>
+      </c>
+      <c r="C19" t="n">
         <v>244</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>147</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>96</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>18</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>136</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>131</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>89</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>74</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>200</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>67</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
@@ -4722,137 +4934,146 @@
       <c r="T19" t="n">
         <v>0</v>
       </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Payments for (Proceeds from) Other Investing Activities</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" t="n">
         <v>5</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>-13</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>3</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>13</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>-10</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>-12</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>-15</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>13</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>-8</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-3</v>
       </c>
       <c r="P20" t="n">
         <v>-3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>-4</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>-5</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>-9</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Investing Activities</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>-323</v>
+      </c>
+      <c r="C21" t="n">
         <v>-115</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>-213</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>-307</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>-174</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>-22938</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>-26183</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>-25477</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>-565</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>-421</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>-103</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>-539</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>-619</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>-309</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>-295</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>-248</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>-122</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>-11009</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>-10963</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>-10987</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Issuance of Long-term Debt</t>
         </is>
@@ -4861,25 +5082,25 @@
         <v>4474</v>
       </c>
       <c r="C22" t="n">
+        <v>4474</v>
+      </c>
+      <c r="D22" t="n">
         <v>10695</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>3735</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>2986</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>34985</v>
-      </c>
-      <c r="G22" t="n">
-        <v>30010</v>
       </c>
       <c r="H22" t="n">
         <v>30010</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>30010</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -4888,16 +5109,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1935</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>1935</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1935</v>
       </c>
       <c r="O22" t="n">
-        <v>9904</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>9904</v>
@@ -4906,44 +5127,47 @@
         <v>9904</v>
       </c>
       <c r="R22" t="n">
+        <v>9904</v>
+      </c>
+      <c r="S22" t="n">
         <v>27802</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>19849</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>15381</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Repayments of Debt</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>-4900</v>
+      </c>
+      <c r="C23" t="n">
         <v>-3650</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>-14840</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-8090</v>
       </c>
       <c r="E23" t="n">
         <v>-8090</v>
       </c>
       <c r="F23" t="n">
+        <v>-8090</v>
+      </c>
+      <c r="G23" t="n">
         <v>-12136</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>-2934</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>-934</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-260</v>
       </c>
       <c r="J23" t="n">
         <v>-260</v>
@@ -4952,35 +5176,38 @@
         <v>-260</v>
       </c>
       <c r="L23" t="n">
-        <v>-2352</v>
+        <v>-260</v>
       </c>
       <c r="M23" t="n">
         <v>-2352</v>
       </c>
       <c r="N23" t="n">
+        <v>-2352</v>
+      </c>
+      <c r="O23" t="n">
         <v>-255</v>
-      </c>
-      <c r="O23" t="n">
-        <v>-10733</v>
       </c>
       <c r="P23" t="n">
         <v>-10733</v>
       </c>
       <c r="Q23" t="n">
+        <v>-10733</v>
+      </c>
+      <c r="R23" t="n">
         <v>-9200</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>-15814</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>-8989</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-4537</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Issuance of Commercial Paper</t>
         </is>
@@ -4989,17 +5216,17 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
         <v>488</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>3861</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>3980</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
@@ -5042,91 +5269,97 @@
       <c r="T24" t="n">
         <v>0</v>
       </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Payments of Dividends</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>-6178</v>
+      </c>
+      <c r="C25" t="n">
         <v>-3086</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>-8345</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>-5559</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>-2774</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>-7330</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>-4878</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>-2435</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>-5741</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>-3840</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>-1926</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-5250</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>-3514</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>-1764</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>-4651</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>-3095</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>-1543</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>-4139</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-2753</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>-1372</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Payments for Repurchase of Common Stock</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>-8450</v>
+      </c>
+      <c r="C26" t="n">
         <v>-7850</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-2450</v>
       </c>
       <c r="D26" t="n">
         <v>-2450</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-2450</v>
       </c>
       <c r="F26" t="n">
-        <v>-7176</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>-7176</v>
@@ -5135,26 +5368,26 @@
         <v>-7176</v>
       </c>
       <c r="I26" t="n">
+        <v>-7176</v>
+      </c>
+      <c r="J26" t="n">
         <v>-5701</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>-3994</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>-1188</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>-7000</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>-5500</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>-2724</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
@@ -5170,9 +5403,12 @@
       <c r="T26" t="n">
         <v>0</v>
       </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
         </is>
@@ -5181,442 +5417,463 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
         <v>-3860</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>-3802</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>-2036</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>-4012</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>-2662</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>-1114</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>-1407</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>-947</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>-333</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>-1181</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>-889</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>-375</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>-1033</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>-686</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>-225</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>-580</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>-388</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>-169</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Proceeds from Issuance of Common Stock</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>113</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>118</v>
+      </c>
+      <c r="E28" t="n">
+        <v>118</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>64</v>
+      </c>
+      <c r="H28" t="n">
+        <v>64</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>63</v>
+      </c>
+      <c r="K28" t="n">
+        <v>63</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>60</v>
+      </c>
+      <c r="N28" t="n">
+        <v>60</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>106</v>
+      </c>
+      <c r="R28" t="n">
+        <v>35</v>
+      </c>
+      <c r="S28" t="n">
+        <v>174</v>
+      </c>
+      <c r="T28" t="n">
+        <v>128</v>
+      </c>
+      <c r="U28" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B29" t="n">
+        <v>-39</v>
+      </c>
+      <c r="C29" t="n">
         <v>-37</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D29" t="n">
         <v>-57</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E29" t="n">
         <v>-50</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F29" t="n">
         <v>-46</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G29" t="n">
         <v>-52</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H29" t="n">
         <v>-16</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I29" t="n">
         <v>-14</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J29" t="n">
         <v>-7</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K29" t="n">
         <v>-2</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L29" t="n">
         <v>5</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M29" t="n">
         <v>-12</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N29" t="n">
         <v>-8</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O29" t="n">
         <v>-4</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P29" t="n">
         <v>-41</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q29" t="n">
         <v>-30</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R29" t="n">
         <v>-28</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S29" t="n">
         <v>-60</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T29" t="n">
         <v>-10</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U29" t="n">
         <v>-4</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B30" t="n">
+        <v>-14980</v>
+      </c>
+      <c r="C30" t="n">
         <v>-10149</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D30" t="n">
         <v>-18251</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E30" t="n">
         <v>-12237</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F30" t="n">
         <v>-5980</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G30" t="n">
         <v>4343</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H30" t="n">
         <v>12408</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I30" t="n">
         <v>18337</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J30" t="n">
         <v>-13053</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K30" t="n">
         <v>-8980</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L30" t="n">
         <v>-3702</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M30" t="n">
         <v>-13800</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N30" t="n">
         <v>-10268</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O30" t="n">
         <v>-5121</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P30" t="n">
         <v>-6441</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q30" t="n">
         <v>-4534</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R30" t="n">
         <v>-1057</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S30" t="n">
         <v>6098</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T30" t="n">
         <v>9580</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U30" t="n">
         <v>10054</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B31" t="n">
+        <v>3450</v>
+      </c>
+      <c r="C31" t="n">
         <v>-2004</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D31" t="n">
         <v>1370</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E31" t="n">
         <v>124</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F31" t="n">
         <v>-41</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G31" t="n">
         <v>-4237</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H31" t="n">
         <v>-4380</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I31" t="n">
         <v>-2325</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J31" t="n">
         <v>-361</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K31" t="n">
         <v>-863</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L31" t="n">
         <v>231</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M31" t="n">
         <v>-2186</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N31" t="n">
         <v>-3158</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O31" t="n">
         <v>-1944</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P31" t="n">
         <v>3487</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q31" t="n">
         <v>1900</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R31" t="n">
         <v>1934</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S31" t="n">
         <v>3802</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T31" t="n">
         <v>4152</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U31" t="n">
         <v>1389</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B32" t="n">
         <v>16178</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C32" t="n">
+        <v>16178</v>
+      </c>
+      <c r="D32" t="n">
         <v>9348</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E32" t="n">
         <v>9348</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F32" t="n">
         <v>9348</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G32" t="n">
         <v>14189</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H32" t="n">
         <v>14189</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I32" t="n">
         <v>14189</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J32" t="n">
         <v>12416</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K32" t="n">
         <v>12416</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L32" t="n">
         <v>12416</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M32" t="n">
         <v>12163</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N32" t="n">
         <v>12163</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O32" t="n">
         <v>12163</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P32" t="n">
         <v>7618</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q32" t="n">
         <v>7618</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R32" t="n">
         <v>7618</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S32" t="n">
         <v>5055</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T32" t="n">
         <v>5055</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U32" t="n">
         <v>5055</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Purchases Of Property And Equipment And Intangible Assets</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
         <v>-25978</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H33" t="n">
         <v>-25976</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I33" t="n">
         <v>-25416</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J33" t="n">
         <v>-17</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>-239</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N33" t="n">
         <v>-234</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>-8</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q33" t="n">
         <v>-8</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R33" t="n">
         <v>-8</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S33" t="n">
         <v>-10872</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T33" t="n">
         <v>-10870</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U33" t="n">
         <v>-10870</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Proceeds from Issuance of Common Stock</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>118</v>
-      </c>
-      <c r="D33" t="n">
-        <v>118</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>64</v>
-      </c>
-      <c r="G33" t="n">
-        <v>64</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>63</v>
-      </c>
-      <c r="J33" t="n">
-        <v>63</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>60</v>
-      </c>
-      <c r="M33" t="n">
-        <v>60</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>113</v>
-      </c>
-      <c r="P33" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>35</v>
-      </c>
-      <c r="R33" t="n">
-        <v>174</v>
-      </c>
-      <c r="S33" t="n">
-        <v>128</v>
-      </c>
-      <c r="T33" t="n">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
